--- a/data/samples/orion_crm_rollout.xlsx
+++ b/data/samples/orion_crm_rollout.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S40"/>
+  <dimension ref="A1:V40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,6 +507,21 @@
           <t>Actual Finish date</t>
         </is>
       </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Effort (hours)</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Effort completed (hours)</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Effort remaining (hours)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -539,12 +554,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P. Ahmed</t>
+          <t>A. Silva</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -577,7 +592,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -589,6 +604,15 @@
         <is>
           <t>2026-01-21</t>
         </is>
+      </c>
+      <c r="T2" t="n">
+        <v>33</v>
+      </c>
+      <c r="U2" t="n">
+        <v>33</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -604,12 +628,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>V. Rao</t>
+          <t>N. Kaur</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -652,8 +676,17 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
-        </is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>80</v>
+      </c>
+      <c r="U3" t="n">
+        <v>80</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -679,12 +712,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>T. Bauer</t>
+          <t>F. Lindqvist</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -717,7 +750,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -729,6 +762,15 @@
         <is>
           <t>2026-02-02</t>
         </is>
+      </c>
+      <c r="T4" t="n">
+        <v>24</v>
+      </c>
+      <c r="U4" t="n">
+        <v>24</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -754,12 +796,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>F. Lindqvist</t>
+          <t>J. Park</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -772,7 +814,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -782,7 +824,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -792,7 +834,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -802,8 +844,17 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
-        </is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>80</v>
+      </c>
+      <c r="U5" t="n">
+        <v>80</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -819,12 +870,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>H. Costa</t>
+          <t>E. Novak</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>PMO</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -837,7 +888,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -857,7 +908,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -867,8 +918,17 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
-        </is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>40</v>
+      </c>
+      <c r="U6" t="n">
+        <v>40</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -902,12 +962,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>N. Kaur</t>
+          <t>P. Ahmed</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -920,7 +980,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -952,6 +1012,15 @@
         <is>
           <t>2026-02-21</t>
         </is>
+      </c>
+      <c r="T7" t="n">
+        <v>24</v>
+      </c>
+      <c r="U7" t="n">
+        <v>24</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -982,7 +1051,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>PMO</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1015,7 +1084,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-14</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1027,6 +1096,15 @@
         <is>
           <t>2026-02-24</t>
         </is>
+      </c>
+      <c r="T8" t="n">
+        <v>32</v>
+      </c>
+      <c r="U8" t="n">
+        <v>32</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1052,12 +1130,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P. Ahmed</t>
+          <t>A. Silva</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>PMO</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1070,7 +1148,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1090,7 +1168,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1100,8 +1178,17 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
-        </is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
+        <v>16</v>
+      </c>
+      <c r="U9" t="n">
+        <v>16</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1117,12 +1204,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>V. Rao</t>
+          <t>N. Kaur</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>PMO</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1135,7 +1222,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1155,7 +1242,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1165,11 +1252,28 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
-        </is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>32</v>
+      </c>
+      <c r="U10" t="n">
+        <v>32</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Approved Budget</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>150000</v>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2.1</t>
@@ -1182,12 +1286,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>T. Bauer</t>
+          <t>F. Lindqvist</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>PMO</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1232,6 +1336,15 @@
         <is>
           <t>2026-03-16</t>
         </is>
+      </c>
+      <c r="T11" t="n">
+        <v>112</v>
+      </c>
+      <c r="U11" t="n">
+        <v>112</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1255,12 +1368,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>F. Lindqvist</t>
+          <t>J. Park</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1273,7 +1386,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1293,7 +1406,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1303,8 +1416,17 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
-        </is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>60</v>
+      </c>
+      <c r="U12" t="n">
+        <v>60</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1442,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>H. Costa</t>
+          <t>E. Novak</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1338,7 +1460,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1348,7 +1470,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1358,7 +1480,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1368,8 +1490,17 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
-        </is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>80</v>
+      </c>
+      <c r="U13" t="n">
+        <v>80</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1385,12 +1516,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>N. Kaur</t>
+          <t>P. Ahmed</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1403,7 +1534,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1413,7 +1544,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1423,7 +1554,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1433,8 +1564,17 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
-        </is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>40</v>
+      </c>
+      <c r="U14" t="n">
+        <v>40</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1455,7 +1595,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1478,7 +1618,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1488,7 +1628,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1498,8 +1638,17 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
-        </is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>24</v>
+      </c>
+      <c r="U15" t="n">
+        <v>24</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1515,7 +1664,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P. Ahmed</t>
+          <t>A. Silva</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1543,7 +1692,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1553,7 +1702,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1563,8 +1712,17 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
-        </is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>44</v>
+      </c>
+      <c r="U16" t="n">
+        <v>44</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1580,12 +1738,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>V. Rao</t>
+          <t>N. Kaur</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>PMO</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1618,7 +1776,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1628,8 +1786,17 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
+        <v>16</v>
+      </c>
+      <c r="U17" t="n">
+        <v>16</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1645,12 +1812,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>T. Bauer</t>
+          <t>F. Lindqvist</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1659,7 +1826,7 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1673,7 +1840,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1683,13 +1850,22 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
+      </c>
+      <c r="T18" t="n">
+        <v>16</v>
+      </c>
+      <c r="U18" t="n">
+        <v>5</v>
+      </c>
+      <c r="V18" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="19">
@@ -1713,7 +1889,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>F. Lindqvist</t>
+          <t>J. Park</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1741,7 +1917,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -1751,7 +1927,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1761,8 +1937,17 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
-        </is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T19" t="n">
+        <v>24</v>
+      </c>
+      <c r="U19" t="n">
+        <v>24</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1778,7 +1963,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>H. Costa</t>
+          <t>E. Novak</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1792,11 +1977,11 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1823,6 +2008,15 @@
         <is>
           <t>2026-04-27</t>
         </is>
+      </c>
+      <c r="T20" t="n">
+        <v>80</v>
+      </c>
+      <c r="U20" t="n">
+        <v>40</v>
+      </c>
+      <c r="V20" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="21">
@@ -1838,12 +2032,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>N. Kaur</t>
+          <t>P. Ahmed</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>PMO</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1878,6 +2072,15 @@
         <is>
           <t>2026-05-03</t>
         </is>
+      </c>
+      <c r="T21" t="n">
+        <v>60</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="22">
@@ -1898,7 +2101,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1933,6 +2136,15 @@
         <is>
           <t>2026-05-08</t>
         </is>
+      </c>
+      <c r="T22" t="n">
+        <v>24</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="23">
@@ -1948,12 +2160,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>P. Ahmed</t>
+          <t>A. Silva</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1988,6 +2200,15 @@
         <is>
           <t>2026-05-14</t>
         </is>
+      </c>
+      <c r="T23" t="n">
+        <v>32</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="24">
@@ -2011,12 +2232,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>V. Rao</t>
+          <t>N. Kaur</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2039,7 +2260,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2051,6 +2272,15 @@
         <is>
           <t>2026-05-19</t>
         </is>
+      </c>
+      <c r="T24" t="n">
+        <v>80</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="25">
@@ -2066,7 +2296,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>T. Bauer</t>
+          <t>F. Lindqvist</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2094,7 +2324,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2106,6 +2336,15 @@
         <is>
           <t>2026-05-25</t>
         </is>
+      </c>
+      <c r="T25" t="n">
+        <v>40</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="26">
@@ -2121,12 +2360,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>F. Lindqvist</t>
+          <t>J. Park</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2161,6 +2400,15 @@
         <is>
           <t>2026-05-30</t>
         </is>
+      </c>
+      <c r="T26" t="n">
+        <v>80</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="27">
@@ -2176,7 +2424,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>H. Costa</t>
+          <t>E. Novak</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2216,6 +2464,15 @@
         <is>
           <t>2026-06-04</t>
         </is>
+      </c>
+      <c r="T27" t="n">
+        <v>80</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="28">
@@ -2231,7 +2488,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>N. Kaur</t>
+          <t>P. Ahmed</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2249,7 +2506,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2271,6 +2528,15 @@
         <is>
           <t>2026-06-10</t>
         </is>
+      </c>
+      <c r="T28" t="n">
+        <v>16</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="29">
@@ -2314,7 +2580,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -2326,6 +2592,15 @@
         <is>
           <t>2026-06-15</t>
         </is>
+      </c>
+      <c r="T29" t="n">
+        <v>22</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="30">
@@ -2341,12 +2616,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P. Ahmed</t>
+          <t>A. Silva</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>PMO</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2381,6 +2656,15 @@
         <is>
           <t>2026-06-21</t>
         </is>
+      </c>
+      <c r="T30" t="n">
+        <v>112</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>112</v>
       </c>
     </row>
     <row r="31">
@@ -2404,12 +2688,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>V. Rao</t>
+          <t>N. Kaur</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>PMO</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2444,6 +2728,15 @@
         <is>
           <t>2026-06-26</t>
         </is>
+      </c>
+      <c r="T31" t="n">
+        <v>16</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="32">
@@ -2459,12 +2752,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>T. Bauer</t>
+          <t>F. Lindqvist</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2477,7 +2770,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2487,7 +2780,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -2499,6 +2792,15 @@
         <is>
           <t>2026-07-01</t>
         </is>
+      </c>
+      <c r="T32" t="n">
+        <v>32</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="33">
@@ -2514,7 +2816,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>F. Lindqvist</t>
+          <t>J. Park</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2554,6 +2856,15 @@
         <is>
           <t>2026-07-07</t>
         </is>
+      </c>
+      <c r="T33" t="n">
+        <v>84</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="34">
@@ -2569,12 +2880,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>H. Costa</t>
+          <t>E. Novak</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>PMO</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2609,6 +2920,15 @@
         <is>
           <t>2026-07-12</t>
         </is>
+      </c>
+      <c r="T34" t="n">
+        <v>56</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>56</v>
       </c>
     </row>
     <row r="35">
@@ -2624,12 +2944,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>N. Kaur</t>
+          <t>P. Ahmed</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2664,6 +2984,15 @@
         <is>
           <t>2026-07-18</t>
         </is>
+      </c>
+      <c r="T35" t="n">
+        <v>33</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="36">
@@ -2692,7 +3021,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>PMO</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2727,6 +3056,15 @@
         <is>
           <t>2026-07-23</t>
         </is>
+      </c>
+      <c r="T36" t="n">
+        <v>84</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="37">
@@ -2742,7 +3080,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>P. Ahmed</t>
+          <t>A. Silva</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2782,6 +3120,15 @@
         <is>
           <t>2026-07-29</t>
         </is>
+      </c>
+      <c r="T37" t="n">
+        <v>32</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="38">
@@ -2797,12 +3144,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>V. Rao</t>
+          <t>N. Kaur</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2815,7 +3162,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2825,7 +3172,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -2837,6 +3184,15 @@
         <is>
           <t>2026-08-03</t>
         </is>
+      </c>
+      <c r="T38" t="n">
+        <v>40</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="39">
@@ -2852,12 +3208,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>T. Bauer</t>
+          <t>F. Lindqvist</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2870,7 +3226,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2892,6 +3248,15 @@
         <is>
           <t>2026-08-08</t>
         </is>
+      </c>
+      <c r="T39" t="n">
+        <v>40</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="40">
@@ -2907,12 +3272,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>F. Lindqvist</t>
+          <t>J. Park</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>PMO</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2925,7 +3290,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2947,6 +3312,15 @@
         <is>
           <t>2026-08-14</t>
         </is>
+      </c>
+      <c r="T40" t="n">
+        <v>32</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
